--- a/2_Formulas_Functions/1_Formulas_Intro.xlsx
+++ b/2_Formulas_Functions/1_Formulas_Intro.xlsx
@@ -8,16 +8,22 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Documents\python\Excel_Data_Analytics\2_Formulas_Functions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30D7E12C-BF3E-4EE5-827D-0CADEA16F717}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5A8A30E-F63A-4CCF-A801-C278B1F44D36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="3" xr2:uid="{8CC555B5-3E06-43B6-9E5B-C0A1D3498DA4}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{8CC555B5-3E06-43B6-9E5B-C0A1D3498DA4}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="1" r:id="rId1"/>
     <sheet name="Math_Operators" sheetId="2" r:id="rId2"/>
     <sheet name="Comparison_Operators" sheetId="3" r:id="rId3"/>
     <sheet name="Cell_Referencing" sheetId="4" r:id="rId4"/>
+    <sheet name="Ex1" sheetId="5" r:id="rId5"/>
+    <sheet name="Task1" sheetId="6" r:id="rId6"/>
+    <sheet name="Task2" sheetId="7" r:id="rId7"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Ex1'!$A$3:$F$3</definedName>
+  </definedNames>
   <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -28,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="66">
   <si>
     <t>Data Scientist</t>
   </si>
@@ -187,6 +193,45 @@
   </si>
   <si>
     <t>Meets Both (1 or 0)</t>
+  </si>
+  <si>
+    <t>Product</t>
+  </si>
+  <si>
+    <t>Original Price</t>
+  </si>
+  <si>
+    <t>Laptop</t>
+  </si>
+  <si>
+    <t>Phone</t>
+  </si>
+  <si>
+    <t>Tablet</t>
+  </si>
+  <si>
+    <t>Monitor</t>
+  </si>
+  <si>
+    <t>Units Sold</t>
+  </si>
+  <si>
+    <t>Unit Price</t>
+  </si>
+  <si>
+    <t>Revenue</t>
+  </si>
+  <si>
+    <t>Keyboard</t>
+  </si>
+  <si>
+    <t>Tax</t>
+  </si>
+  <si>
+    <t>Final Price</t>
+  </si>
+  <si>
+    <t>Price</t>
   </si>
 </sst>
 </file>
@@ -403,7 +448,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -479,6 +524,42 @@
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -822,11 +903,14 @@
     <col min="2" max="2" width="22.7109375" style="4" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10.42578125" style="4" customWidth="1"/>
     <col min="4" max="4" width="12.28515625" style="4" customWidth="1"/>
-    <col min="5" max="5" width="11.5703125" style="4" customWidth="1"/>
-    <col min="6" max="6" width="10" style="4" customWidth="1"/>
-    <col min="7" max="7" width="9" style="4"/>
-    <col min="8" max="8" width="9" style="30"/>
-    <col min="9" max="13" width="9" style="4"/>
+    <col min="5" max="5" width="21" style="4" customWidth="1"/>
+    <col min="6" max="6" width="15.42578125" style="4" hidden="1" customWidth="1"/>
+    <col min="7" max="7" width="16.42578125" style="4" customWidth="1"/>
+    <col min="8" max="8" width="16.85546875" style="30" hidden="1" customWidth="1"/>
+    <col min="9" max="9" width="14.7109375" style="4" customWidth="1"/>
+    <col min="10" max="10" width="23.42578125" style="4" hidden="1" customWidth="1"/>
+    <col min="11" max="11" width="15.7109375" style="4" hidden="1" customWidth="1"/>
+    <col min="12" max="13" width="9" style="4"/>
     <col min="14" max="14" width="11.28515625" style="4" customWidth="1"/>
     <col min="15" max="16384" width="9" style="4"/>
   </cols>
@@ -902,7 +986,7 @@
         <v>8.3333333333333329E-2</v>
       </c>
       <c r="I3" s="4">
-        <f>H3 * D3 +D3</f>
+        <f>H3 *D3 +D3</f>
         <v>130000</v>
       </c>
       <c r="J3" s="4" t="b">
@@ -910,8 +994,24 @@
         <v>1</v>
       </c>
       <c r="K3" s="4" t="b">
-        <f>E3 &gt; D3</f>
-        <v>0</v>
+        <f>E3 &gt;D3</f>
+        <v>0</v>
+      </c>
+      <c r="L3" s="4" t="b">
+        <f>$C$15 &lt;= $C3</f>
+        <v>1</v>
+      </c>
+      <c r="M3" s="4" t="b">
+        <f>$G3 &gt;= $C$16</f>
+        <v>1</v>
+      </c>
+      <c r="N3" s="4">
+        <f>L3 * M3</f>
+        <v>1</v>
+      </c>
+      <c r="O3" s="4" t="b">
+        <f>L3 *M3=1</f>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="2:15" x14ac:dyDescent="0.25">
@@ -940,7 +1040,7 @@
         <v>8.8888888888888892E-2</v>
       </c>
       <c r="I4" s="4">
-        <f t="shared" ref="I4:I12" si="3">H4 * D4 +D4</f>
+        <f t="shared" ref="I4:I12" si="3">H4 *D4 +D4</f>
         <v>147000</v>
       </c>
       <c r="J4" s="4" t="b">
@@ -948,7 +1048,23 @@
         <v>1</v>
       </c>
       <c r="K4" s="4" t="b">
-        <f t="shared" ref="K4:K12" si="5">E4 &gt; D4</f>
+        <f t="shared" ref="K4:K12" si="5">E4 &gt;D4</f>
+        <v>0</v>
+      </c>
+      <c r="L4" s="4" t="b">
+        <f>$C$15 &lt;= $C4</f>
+        <v>0</v>
+      </c>
+      <c r="M4" s="4" t="b">
+        <f t="shared" ref="M4:M12" si="6">$G4 &gt;= $C$16</f>
+        <v>1</v>
+      </c>
+      <c r="N4" s="4">
+        <f t="shared" ref="N4:N12" si="7">L4 * M4</f>
+        <v>0</v>
+      </c>
+      <c r="O4" s="4" t="b">
+        <f t="shared" ref="O4:O12" si="8">L4 *M4=1</f>
         <v>0</v>
       </c>
     </row>
@@ -989,6 +1105,22 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
+      <c r="L5" s="4" t="b">
+        <f>$C$15 &lt;= $C5</f>
+        <v>0</v>
+      </c>
+      <c r="M5" s="4" t="b">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="N5" s="4">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="O5" s="4" t="b">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="6" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B6" s="8" t="s">
@@ -1027,6 +1159,22 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
+      <c r="L6" s="4" t="b">
+        <f>$C$15 &lt;= $C6</f>
+        <v>1</v>
+      </c>
+      <c r="M6" s="4" t="b">
+        <f t="shared" si="6"/>
+        <v>1</v>
+      </c>
+      <c r="N6" s="4">
+        <f t="shared" si="7"/>
+        <v>1</v>
+      </c>
+      <c r="O6" s="4" t="b">
+        <f t="shared" si="8"/>
+        <v>1</v>
+      </c>
     </row>
     <row r="7" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B7" s="8" t="s">
@@ -1065,6 +1213,22 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
+      <c r="L7" s="4" t="b">
+        <f>$C$15 &lt;= $C7</f>
+        <v>0</v>
+      </c>
+      <c r="M7" s="4" t="b">
+        <f t="shared" si="6"/>
+        <v>1</v>
+      </c>
+      <c r="N7" s="4">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="O7" s="4" t="b">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="8" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B8" s="8" t="s">
@@ -1103,6 +1267,22 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
+      <c r="L8" s="4" t="b">
+        <f t="shared" ref="L8:L10" si="9">$C$15 &lt;= $C8</f>
+        <v>1</v>
+      </c>
+      <c r="M8" s="4" t="b">
+        <f t="shared" si="6"/>
+        <v>1</v>
+      </c>
+      <c r="N8" s="4">
+        <f t="shared" si="7"/>
+        <v>1</v>
+      </c>
+      <c r="O8" s="4" t="b">
+        <f t="shared" si="8"/>
+        <v>1</v>
+      </c>
     </row>
     <row r="9" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B9" s="8" t="s">
@@ -1141,6 +1321,22 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
+      <c r="L9" s="4" t="b">
+        <f t="shared" si="9"/>
+        <v>1</v>
+      </c>
+      <c r="M9" s="4" t="b">
+        <f t="shared" si="6"/>
+        <v>1</v>
+      </c>
+      <c r="N9" s="4">
+        <f t="shared" si="7"/>
+        <v>1</v>
+      </c>
+      <c r="O9" s="4" t="b">
+        <f t="shared" si="8"/>
+        <v>1</v>
+      </c>
     </row>
     <row r="10" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B10" s="8" t="s">
@@ -1179,6 +1375,22 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
+      <c r="L10" s="4" t="b">
+        <f t="shared" si="9"/>
+        <v>1</v>
+      </c>
+      <c r="M10" s="4" t="b">
+        <f t="shared" si="6"/>
+        <v>1</v>
+      </c>
+      <c r="N10" s="4">
+        <f t="shared" si="7"/>
+        <v>1</v>
+      </c>
+      <c r="O10" s="4" t="b">
+        <f t="shared" si="8"/>
+        <v>1</v>
+      </c>
     </row>
     <row r="11" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B11" s="8" t="s">
@@ -1217,6 +1429,22 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
+      <c r="L11" s="4" t="b">
+        <f>$C$15 &lt;= $C11</f>
+        <v>0</v>
+      </c>
+      <c r="M11" s="4" t="b">
+        <f t="shared" si="6"/>
+        <v>1</v>
+      </c>
+      <c r="N11" s="4">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="O11" s="4" t="b">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="12" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B12" s="11" t="s">
@@ -1255,6 +1483,22 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
+      <c r="L12" s="4" t="b">
+        <f>$C$15 &lt;= $C12</f>
+        <v>1</v>
+      </c>
+      <c r="M12" s="4" t="b">
+        <f t="shared" si="6"/>
+        <v>1</v>
+      </c>
+      <c r="N12" s="4">
+        <f t="shared" si="7"/>
+        <v>1</v>
+      </c>
+      <c r="O12" s="4" t="b">
+        <f>L12 *M12=1</f>
+        <v>1</v>
+      </c>
     </row>
     <row r="14" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B14" s="29" t="s">
@@ -1265,13 +1509,17 @@
       <c r="B15" s="25" t="s">
         <v>48</v>
       </c>
-      <c r="C15" s="26"/>
+      <c r="C15" s="26">
+        <v>5</v>
+      </c>
     </row>
     <row r="16" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B16" s="27" t="s">
         <v>49</v>
       </c>
-      <c r="C16" s="28"/>
+      <c r="C16" s="28">
+        <v>90000</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2309,19 +2557,19 @@
         <v>0</v>
       </c>
       <c r="L4" s="4" t="b">
-        <f t="shared" ref="L4:L12" si="6">$C$15&lt;=C4</f>
+        <f t="shared" ref="L4:L5" si="6">$C$15&lt;=C4</f>
         <v>0</v>
       </c>
       <c r="M4" s="4" t="b">
-        <f t="shared" ref="M4:M12" si="7">$G4&gt;=$C$16</f>
+        <f>$G4&gt;=$C$16</f>
         <v>1</v>
       </c>
       <c r="N4" s="4">
-        <f t="shared" ref="N4:N12" si="8">L4*M4</f>
+        <f>L4*M4</f>
         <v>0</v>
       </c>
       <c r="O4" s="4" t="b">
-        <f t="shared" ref="O4:O12" si="9">L4*M4=1</f>
+        <f t="shared" ref="O4:O12" si="7">L4*M4=1</f>
         <v>0</v>
       </c>
     </row>
@@ -2367,15 +2615,15 @@
         <v>0</v>
       </c>
       <c r="M5" s="4" t="b">
+        <f>$G5&gt;=$C$16</f>
+        <v>0</v>
+      </c>
+      <c r="N5" s="4">
+        <f t="shared" ref="N4:N12" si="8">L5*M5</f>
+        <v>0</v>
+      </c>
+      <c r="O5" s="4" t="b">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="N5" s="4">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="O5" s="4" t="b">
-        <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
@@ -2417,11 +2665,11 @@
         <v>0</v>
       </c>
       <c r="L6" s="4" t="b">
-        <f t="shared" si="6"/>
+        <f t="shared" ref="L6:L12" si="9">$C$15&lt;=C6</f>
         <v>1</v>
       </c>
       <c r="M6" s="4" t="b">
-        <f t="shared" si="7"/>
+        <f>$G6&gt;=$C$16</f>
         <v>1</v>
       </c>
       <c r="N6" s="4">
@@ -2429,7 +2677,7 @@
         <v>1</v>
       </c>
       <c r="O6" s="4" t="b">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
     </row>
@@ -2471,11 +2719,11 @@
         <v>0</v>
       </c>
       <c r="L7" s="4" t="b">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="M7" s="4" t="b">
-        <f t="shared" si="7"/>
+        <f>$G7&gt;=$C$16</f>
         <v>1</v>
       </c>
       <c r="N7" s="4">
@@ -2483,7 +2731,7 @@
         <v>0</v>
       </c>
       <c r="O7" s="4" t="b">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
@@ -2525,11 +2773,11 @@
         <v>0</v>
       </c>
       <c r="L8" s="4" t="b">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="M8" s="4" t="b">
-        <f t="shared" si="7"/>
+        <f t="shared" ref="M8" si="10">$G8&gt;=$C$16</f>
         <v>1</v>
       </c>
       <c r="N8" s="4">
@@ -2537,7 +2785,7 @@
         <v>1</v>
       </c>
       <c r="O8" s="4" t="b">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
     </row>
@@ -2579,11 +2827,11 @@
         <v>0</v>
       </c>
       <c r="L9" s="4" t="b">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="M9" s="4" t="b">
-        <f t="shared" si="7"/>
+        <f>$G9&gt;=$C$16</f>
         <v>1</v>
       </c>
       <c r="N9" s="4">
@@ -2591,7 +2839,7 @@
         <v>1</v>
       </c>
       <c r="O9" s="4" t="b">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
     </row>
@@ -2613,7 +2861,7 @@
         <v>8</v>
       </c>
       <c r="G10" s="4">
-        <f t="shared" si="1"/>
+        <f>D10+E10</f>
         <v>143000</v>
       </c>
       <c r="H10" s="15">
@@ -2633,11 +2881,11 @@
         <v>0</v>
       </c>
       <c r="L10" s="4" t="b">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="M10" s="4" t="b">
-        <f t="shared" si="7"/>
+        <f>$G10&gt;=$C$16</f>
         <v>1</v>
       </c>
       <c r="N10" s="4">
@@ -2645,7 +2893,7 @@
         <v>1</v>
       </c>
       <c r="O10" s="4" t="b">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
     </row>
@@ -2687,11 +2935,11 @@
         <v>0</v>
       </c>
       <c r="L11" s="4" t="b">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="M11" s="4" t="b">
-        <f t="shared" si="7"/>
+        <f>$G11&gt;=$C$16</f>
         <v>1</v>
       </c>
       <c r="N11" s="4">
@@ -2699,7 +2947,7 @@
         <v>0</v>
       </c>
       <c r="O11" s="4" t="b">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
@@ -2741,11 +2989,11 @@
         <v>0</v>
       </c>
       <c r="L12" s="4" t="b">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="M12" s="4" t="b">
-        <f t="shared" si="7"/>
+        <f>$G12&gt;=$C$16</f>
         <v>1</v>
       </c>
       <c r="N12" s="4">
@@ -2753,7 +3001,7 @@
         <v>1</v>
       </c>
       <c r="O12" s="4" t="b">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
     </row>
@@ -2776,6 +3024,439 @@
       </c>
       <c r="C16" s="28">
         <v>90000</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2C9A87B6-44A9-462D-93D0-970049346E59}">
+  <dimension ref="A3:F7"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="3" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="A3" s="32" t="s">
+        <v>53</v>
+      </c>
+      <c r="B3" s="34" t="s">
+        <v>54</v>
+      </c>
+      <c r="C3" s="35">
+        <v>0.05</v>
+      </c>
+      <c r="D3" s="35">
+        <v>0.1</v>
+      </c>
+      <c r="E3" s="35">
+        <v>0.15</v>
+      </c>
+      <c r="F3" s="35">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="36" t="s">
+        <v>55</v>
+      </c>
+      <c r="B4" s="38">
+        <v>500000</v>
+      </c>
+      <c r="C4" s="33">
+        <f>$B4 * C$3</f>
+        <v>25000</v>
+      </c>
+      <c r="D4" s="33">
+        <f>$B4 * D$3</f>
+        <v>50000</v>
+      </c>
+      <c r="E4" s="33">
+        <f>$B4 * E$3</f>
+        <v>75000</v>
+      </c>
+      <c r="F4" s="33">
+        <f>$B4 * F$3</f>
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="36" t="s">
+        <v>56</v>
+      </c>
+      <c r="B5" s="37">
+        <v>250000</v>
+      </c>
+      <c r="C5" s="33">
+        <f t="shared" ref="C5:F7" si="0">$B5 * C$3</f>
+        <v>12500</v>
+      </c>
+      <c r="D5" s="33">
+        <f t="shared" si="0"/>
+        <v>25000</v>
+      </c>
+      <c r="E5" s="33">
+        <f t="shared" si="0"/>
+        <v>37500</v>
+      </c>
+      <c r="F5" s="33">
+        <f t="shared" si="0"/>
+        <v>50000</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="36" t="s">
+        <v>57</v>
+      </c>
+      <c r="B6" s="37">
+        <v>180000</v>
+      </c>
+      <c r="C6" s="33">
+        <f t="shared" si="0"/>
+        <v>9000</v>
+      </c>
+      <c r="D6" s="33">
+        <f t="shared" si="0"/>
+        <v>18000</v>
+      </c>
+      <c r="E6" s="33">
+        <f t="shared" si="0"/>
+        <v>27000</v>
+      </c>
+      <c r="F6" s="33">
+        <f t="shared" si="0"/>
+        <v>36000</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="36" t="s">
+        <v>58</v>
+      </c>
+      <c r="B7" s="37">
+        <v>300000</v>
+      </c>
+      <c r="C7" s="33">
+        <f t="shared" si="0"/>
+        <v>15000</v>
+      </c>
+      <c r="D7" s="33">
+        <f t="shared" si="0"/>
+        <v>30000</v>
+      </c>
+      <c r="E7" s="33">
+        <f t="shared" si="0"/>
+        <v>45000</v>
+      </c>
+      <c r="F7" s="33">
+        <f t="shared" si="0"/>
+        <v>60000</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{76367626-FCFA-4BDF-80A2-671C1E0E50D2}">
+  <dimension ref="A1:G6"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="4" width="15.140625" customWidth="1"/>
+    <col min="5" max="5" width="9.140625" style="42"/>
+    <col min="6" max="6" width="0" style="42" hidden="1" customWidth="1"/>
+    <col min="7" max="7" width="9.140625" style="42"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="32" t="s">
+        <v>53</v>
+      </c>
+      <c r="B1" s="32" t="s">
+        <v>59</v>
+      </c>
+      <c r="C1" s="32" t="s">
+        <v>60</v>
+      </c>
+      <c r="D1" s="32" t="s">
+        <v>61</v>
+      </c>
+      <c r="E1" s="41" t="s">
+        <v>63</v>
+      </c>
+      <c r="F1" s="40">
+        <v>7.4999999999999997E-2</v>
+      </c>
+      <c r="G1" s="41" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="36" t="s">
+        <v>55</v>
+      </c>
+      <c r="B2" s="33">
+        <v>5</v>
+      </c>
+      <c r="C2" s="37">
+        <v>450000</v>
+      </c>
+      <c r="D2" s="33">
+        <f>C2  * B2</f>
+        <v>2250000</v>
+      </c>
+      <c r="E2" s="42">
+        <f>D2 * $F$1</f>
+        <v>168750</v>
+      </c>
+      <c r="G2" s="42">
+        <f>D2 + E2</f>
+        <v>2418750</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="36" t="s">
+        <v>56</v>
+      </c>
+      <c r="B3" s="33">
+        <v>10</v>
+      </c>
+      <c r="C3" s="37">
+        <v>250000</v>
+      </c>
+      <c r="D3" s="33">
+        <f t="shared" ref="D3:D6" si="0">C3  * B3</f>
+        <v>2500000</v>
+      </c>
+      <c r="E3" s="42">
+        <f t="shared" ref="E3:E6" si="1">D3 * $F$1</f>
+        <v>187500</v>
+      </c>
+      <c r="G3" s="42">
+        <f>D3 + E3</f>
+        <v>2687500</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="36" t="s">
+        <v>57</v>
+      </c>
+      <c r="B4" s="33">
+        <v>8</v>
+      </c>
+      <c r="C4" s="37">
+        <v>180000</v>
+      </c>
+      <c r="D4" s="33">
+        <f t="shared" si="0"/>
+        <v>1440000</v>
+      </c>
+      <c r="E4" s="42">
+        <f>D4 * $F$1</f>
+        <v>108000</v>
+      </c>
+      <c r="G4" s="42">
+        <f t="shared" ref="G4:G6" si="2">D4 + E4</f>
+        <v>1548000</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="36" t="s">
+        <v>58</v>
+      </c>
+      <c r="B5" s="33">
+        <v>6</v>
+      </c>
+      <c r="C5" s="37">
+        <v>300000</v>
+      </c>
+      <c r="D5" s="33">
+        <f t="shared" si="0"/>
+        <v>1800000</v>
+      </c>
+      <c r="E5" s="42">
+        <f t="shared" si="1"/>
+        <v>135000</v>
+      </c>
+      <c r="G5" s="42">
+        <f t="shared" si="2"/>
+        <v>1935000</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="36" t="s">
+        <v>62</v>
+      </c>
+      <c r="B6" s="33">
+        <v>20</v>
+      </c>
+      <c r="C6" s="37">
+        <v>25000</v>
+      </c>
+      <c r="D6" s="33">
+        <f t="shared" si="0"/>
+        <v>500000</v>
+      </c>
+      <c r="E6" s="42">
+        <f t="shared" si="1"/>
+        <v>37500</v>
+      </c>
+      <c r="G6" s="42">
+        <f t="shared" si="2"/>
+        <v>537500</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{857290FD-BDE9-40D3-9771-F15D502B3655}">
+  <dimension ref="A1:F6"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="6" width="14.42578125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="32" t="s">
+        <v>53</v>
+      </c>
+      <c r="B1" s="34" t="s">
+        <v>65</v>
+      </c>
+      <c r="C1" s="39">
+        <v>0.05</v>
+      </c>
+      <c r="D1" s="39">
+        <v>0.1</v>
+      </c>
+      <c r="E1" s="39">
+        <v>0.15</v>
+      </c>
+      <c r="F1" s="39">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="36" t="s">
+        <v>55</v>
+      </c>
+      <c r="B2" s="37">
+        <v>450000</v>
+      </c>
+      <c r="C2" s="43">
+        <f>B2 * $C$1</f>
+        <v>22500</v>
+      </c>
+      <c r="D2" s="33">
+        <f>B2*$D$1</f>
+        <v>45000</v>
+      </c>
+      <c r="E2" s="33">
+        <f>B2 *$E$1</f>
+        <v>67500</v>
+      </c>
+      <c r="F2" s="33">
+        <f>B2* $F$1</f>
+        <v>90000</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="36" t="s">
+        <v>56</v>
+      </c>
+      <c r="B3" s="37">
+        <v>250000</v>
+      </c>
+      <c r="C3" s="43">
+        <f t="shared" ref="C3:C6" si="0">B3 * $C$1</f>
+        <v>12500</v>
+      </c>
+      <c r="D3" s="33">
+        <f t="shared" ref="D3:D6" si="1">B3*$D$1</f>
+        <v>25000</v>
+      </c>
+      <c r="E3" s="33">
+        <f t="shared" ref="E3:E6" si="2">B3 *$E$1</f>
+        <v>37500</v>
+      </c>
+      <c r="F3" s="33">
+        <f t="shared" ref="F3:F6" si="3">B3* $F$1</f>
+        <v>50000</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="36" t="s">
+        <v>57</v>
+      </c>
+      <c r="B4" s="37">
+        <v>180000</v>
+      </c>
+      <c r="C4" s="43">
+        <f t="shared" si="0"/>
+        <v>9000</v>
+      </c>
+      <c r="D4" s="33">
+        <f t="shared" si="1"/>
+        <v>18000</v>
+      </c>
+      <c r="E4" s="33">
+        <f t="shared" si="2"/>
+        <v>27000</v>
+      </c>
+      <c r="F4" s="33">
+        <f t="shared" si="3"/>
+        <v>36000</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="36" t="s">
+        <v>58</v>
+      </c>
+      <c r="B5" s="37">
+        <v>300000</v>
+      </c>
+      <c r="C5" s="43">
+        <f t="shared" si="0"/>
+        <v>15000</v>
+      </c>
+      <c r="D5" s="33">
+        <f t="shared" si="1"/>
+        <v>30000</v>
+      </c>
+      <c r="E5" s="33">
+        <f t="shared" si="2"/>
+        <v>45000</v>
+      </c>
+      <c r="F5" s="33">
+        <f t="shared" si="3"/>
+        <v>60000</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="36" t="s">
+        <v>62</v>
+      </c>
+      <c r="B6" s="37">
+        <v>25000</v>
+      </c>
+      <c r="C6" s="43">
+        <f t="shared" si="0"/>
+        <v>1250</v>
+      </c>
+      <c r="D6" s="33">
+        <f t="shared" si="1"/>
+        <v>2500</v>
+      </c>
+      <c r="E6" s="33">
+        <f t="shared" si="2"/>
+        <v>3750</v>
+      </c>
+      <c r="F6" s="33">
+        <f t="shared" si="3"/>
+        <v>5000</v>
       </c>
     </row>
   </sheetData>
